--- a/chapter5/variatie.xlsx
+++ b/chapter5/variatie.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20339"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\u0146408\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jelle\Documents\DoctoraatLocal\algorithms-course\algorithms-course-student\chapter5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C000F91-04DC-4E2E-A0BA-B67432AB69FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98665336-2734-459C-A5E9-ED2B29B0DDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17625" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15384" yWindow="792" windowWidth="15336" windowHeight="10776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,15 +26,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="434">
   <si>
     <t xml:space="preserve">Datum </t>
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y </t>
   </si>
   <si>
     <t>Z</t>
@@ -1373,10 +1370,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1395,9 +1392,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1435,7 +1432,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1541,7 +1538,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1683,7 +1680,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1692,13 +1689,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D120"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1706,13 +1703,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>43539</v>
       </c>
@@ -1726,7 +1723,7 @@
         <v>886.03750417038498</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>43540</v>
       </c>
@@ -1740,7 +1737,7 @@
         <v>961.32864481097101</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>43541</v>
       </c>
@@ -1754,7 +1751,7 @@
         <v>450.05214837566598</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>43542</v>
       </c>
@@ -1768,7 +1765,7 @@
         <v>448.63420114651097</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>43543</v>
       </c>
@@ -1782,7 +1779,7 @@
         <v>105.528208755309</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>43544</v>
       </c>
@@ -1796,7 +1793,7 @@
         <v>396.771576830784</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>43545</v>
       </c>
@@ -1810,7 +1807,7 @@
         <v>129.57271532571201</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>43546</v>
       </c>
@@ -1824,7 +1821,7 @@
         <v>681.77079106100098</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>43547</v>
       </c>
@@ -1838,7 +1835,7 @@
         <v>147.34709328252299</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>43548</v>
       </c>
@@ -1852,7 +1849,7 @@
         <v>337.93361962813202</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>43549</v>
       </c>
@@ -1866,7 +1863,7 @@
         <v>311.697566222533</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>43550</v>
       </c>
@@ -1880,7 +1877,7 @@
         <v>229.63769067682199</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>43551</v>
       </c>
@@ -1894,7 +1891,7 @@
         <v>110.505612263236</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>43552</v>
       </c>
@@ -1908,7 +1905,7 @@
         <v>466.20691014129602</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>43553</v>
       </c>
@@ -1922,7 +1919,7 @@
         <v>329.596359749513</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>43554</v>
       </c>
@@ -1936,7 +1933,7 @@
         <v>872.65853459360596</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>43555</v>
       </c>
@@ -1950,7 +1947,7 @@
         <v>858.03906042173105</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>43556</v>
       </c>
@@ -1964,7 +1961,7 @@
         <v>577.38306212633597</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>43557</v>
       </c>
@@ -1978,7 +1975,7 @@
         <v>83.365484100516099</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>43558</v>
       </c>
@@ -1992,7 +1989,7 @@
         <v>564.57896266883199</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>43559</v>
       </c>
@@ -2006,7 +2003,7 @@
         <v>814.29511051043596</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>43560</v>
       </c>
@@ -2020,7 +2017,7 @@
         <v>114.65262355225801</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>43561</v>
       </c>
@@ -2034,7 +2031,7 @@
         <v>968.19038094573796</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>43562</v>
       </c>
@@ -2048,7 +2045,7 @@
         <v>848.80730441957405</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>43563</v>
       </c>
@@ -2062,7 +2059,7 @@
         <v>717.79434362070594</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>43564</v>
       </c>
@@ -2076,7 +2073,7 @@
         <v>483.61428470721501</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>43565</v>
       </c>
@@ -2090,7 +2087,7 @@
         <v>563.99432874981005</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>43566</v>
       </c>
@@ -2104,7 +2101,7 @@
         <v>866.58797477530504</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>43567</v>
       </c>
@@ -2118,7 +2115,7 @@
         <v>502.63608424346597</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>43568</v>
       </c>
@@ -2132,7 +2129,7 @@
         <v>239.354812420684</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>43569</v>
       </c>
@@ -2146,7 +2143,7 @@
         <v>208.978202518665</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>43570</v>
       </c>
@@ -2160,7 +2157,7 @@
         <v>764.79838665866998</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>43571</v>
       </c>
@@ -2174,7 +2171,7 @@
         <v>900.77872719100105</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>43572</v>
       </c>
@@ -2188,7 +2185,7 @@
         <v>346.99546485998098</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>43573</v>
       </c>
@@ -2202,7 +2199,7 @@
         <v>620.92238754539096</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>43574</v>
       </c>
@@ -2216,7 +2213,7 @@
         <v>319.33740519941398</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>43575</v>
       </c>
@@ -2230,7 +2227,7 @@
         <v>773.52487267513197</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>43576</v>
       </c>
@@ -2244,7 +2241,7 @@
         <v>96.662950114535207</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>43577</v>
       </c>
@@ -2258,7 +2255,7 @@
         <v>640.33108562747805</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>43578</v>
       </c>
@@ -2272,7 +2269,7 @@
         <v>985.20949757088704</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>43579</v>
       </c>
@@ -2286,7 +2283,7 @@
         <v>665.94621304493398</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>43580</v>
       </c>
@@ -2300,7 +2297,7 @@
         <v>524.02064243141297</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43581</v>
       </c>
@@ -2314,7 +2311,7 @@
         <v>656.38838087111606</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43582</v>
       </c>
@@ -2328,7 +2325,7 @@
         <v>916.23178212743096</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>43583</v>
       </c>
@@ -2342,7 +2339,7 @@
         <v>790.66173726519298</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>43584</v>
       </c>
@@ -2356,7 +2353,7 @@
         <v>251.17763185665601</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>43585</v>
       </c>
@@ -2370,7 +2367,7 @@
         <v>388.57718704697101</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>43586</v>
       </c>
@@ -2384,7 +2381,7 @@
         <v>620.24986043227796</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>43587</v>
       </c>
@@ -2398,7 +2395,7 @@
         <v>241.47029484449899</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>43588</v>
       </c>
@@ -2412,7 +2409,7 @@
         <v>675.71036995321197</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>43589</v>
       </c>
@@ -2426,7 +2423,7 @@
         <v>738.28965539696605</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>43590</v>
       </c>
@@ -2440,7 +2437,7 @@
         <v>256.90840679256598</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>43591</v>
       </c>
@@ -2454,7 +2451,7 @@
         <v>485.721545765587</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>43592</v>
       </c>
@@ -2468,7 +2465,7 @@
         <v>149.462495849964</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>43593</v>
       </c>
@@ -2482,7 +2479,7 @@
         <v>365.439234829562</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>43594</v>
       </c>
@@ -2496,7 +2493,7 @@
         <v>617.65451969332003</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>43595</v>
       </c>
@@ -2510,7 +2507,7 @@
         <v>668.31199553847898</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>43596</v>
       </c>
@@ -2524,7 +2521,7 @@
         <v>739.41085696485004</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>43597</v>
       </c>
@@ -2538,7 +2535,7 @@
         <v>537.67582400840104</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>43598</v>
       </c>
@@ -2552,7 +2549,7 @@
         <v>686.66338683738695</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>43599</v>
       </c>
@@ -2566,7 +2563,7 @@
         <v>388.19678148042601</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>43600</v>
       </c>
@@ -2580,7 +2577,7 @@
         <v>526.64570247699396</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>43601</v>
       </c>
@@ -2594,7 +2591,7 @@
         <v>706.91517110949303</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>43602</v>
       </c>
@@ -2608,7 +2605,7 @@
         <v>71.908383477820905</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>43603</v>
       </c>
@@ -2622,7 +2619,7 @@
         <v>617.91081938219202</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>43604</v>
       </c>
@@ -2636,7 +2633,7 @@
         <v>33.081965157371798</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>43605</v>
       </c>
@@ -2650,7 +2647,7 @@
         <v>263.74789823064998</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>43606</v>
       </c>
@@ -2664,7 +2661,7 @@
         <v>448.25908766582597</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>43607</v>
       </c>
@@ -2678,7 +2675,7 @@
         <v>257.05186765014798</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>43608</v>
       </c>
@@ -2692,7 +2689,7 @@
         <v>380.31979759790897</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>43609</v>
       </c>
@@ -2706,7 +2703,7 @@
         <v>125.414862048985</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>43610</v>
       </c>
@@ -2720,7 +2717,7 @@
         <v>805.14125621437904</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>43611</v>
       </c>
@@ -2734,7 +2731,7 @@
         <v>223.01733303493901</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>43612</v>
       </c>
@@ -2748,7 +2745,7 @@
         <v>893.33165744568805</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>43613</v>
       </c>
@@ -2762,7 +2759,7 @@
         <v>422.31989753786399</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>43614</v>
       </c>
@@ -2776,7 +2773,7 @@
         <v>510.09942960670497</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>43615</v>
       </c>
@@ -2790,7 +2787,7 @@
         <v>317.77677087822298</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>43616</v>
       </c>
@@ -2804,7 +2801,7 @@
         <v>562.173164192238</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>43617</v>
       </c>
@@ -2818,7 +2815,7 @@
         <v>123.109840236172</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>43618</v>
       </c>
@@ -2832,7 +2829,7 @@
         <v>322.40296379461898</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>43619</v>
       </c>
@@ -2846,7 +2843,7 @@
         <v>509.86667222396898</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>43620</v>
       </c>
@@ -2860,7 +2857,7 @@
         <v>581.74249472841598</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>43621</v>
       </c>
@@ -2874,7 +2871,7 @@
         <v>114.669462722399</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>43622</v>
       </c>
@@ -2888,7 +2885,7 @@
         <v>159.609868634809</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>43623</v>
       </c>
@@ -2902,7 +2899,7 @@
         <v>165.810022601931</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>43624</v>
       </c>
@@ -2916,7 +2913,7 @@
         <v>31.753969526705401</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>43625</v>
       </c>
@@ -2930,7 +2927,7 @@
         <v>942.26368130106505</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>43626</v>
       </c>
@@ -2944,7 +2941,7 @@
         <v>716.71204395290499</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>43627</v>
       </c>
@@ -2958,7 +2955,7 @@
         <v>477.70846519817701</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>43628</v>
       </c>
@@ -2972,7 +2969,7 @@
         <v>558.96884830200202</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>43629</v>
       </c>
@@ -2986,7 +2983,7 @@
         <v>864.98213821541594</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>43630</v>
       </c>
@@ -3000,7 +2997,7 @@
         <v>440.56811167562802</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>43631</v>
       </c>
@@ -3014,7 +3011,7 @@
         <v>78.514410625763901</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>43632</v>
       </c>
@@ -3028,7 +3025,7 @@
         <v>862.26854563881295</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>43633</v>
       </c>
@@ -3042,7 +3039,7 @@
         <v>199.17239068101199</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>43634</v>
       </c>
@@ -3056,7 +3053,7 @@
         <v>890.35893617053398</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>43635</v>
       </c>
@@ -3070,7 +3067,7 @@
         <v>738.49140158818705</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>43636</v>
       </c>
@@ -3084,7 +3081,7 @@
         <v>632.47333714426702</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>43637</v>
       </c>
@@ -3098,7 +3095,7 @@
         <v>491.76722840391102</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>43638</v>
       </c>
@@ -3112,7 +3109,7 @@
         <v>926.58622253136605</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>43639</v>
       </c>
@@ -3126,7 +3123,7 @@
         <v>98.089240765404398</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>43640</v>
       </c>
@@ -3140,7 +3137,7 @@
         <v>119.850007453679</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>43641</v>
       </c>
@@ -3154,7 +3151,7 @@
         <v>404.57889282413299</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>43642</v>
       </c>
@@ -3168,7 +3165,7 @@
         <v>68.444426958186199</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>43643</v>
       </c>
@@ -3182,7 +3179,7 @@
         <v>31.316238481323499</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>43644</v>
       </c>
@@ -3196,7 +3193,7 @@
         <v>296.30964404295298</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>43645</v>
       </c>
@@ -3210,7 +3207,7 @@
         <v>779.91626062149805</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>43646</v>
       </c>
@@ -3224,7 +3221,7 @@
         <v>486.97987770449902</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>43647</v>
       </c>
@@ -3238,7 +3235,7 @@
         <v>213.96295119336199</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>43648</v>
       </c>
@@ -3252,7 +3249,7 @@
         <v>445.93852449729599</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>43649</v>
       </c>
@@ -3266,7 +3263,7 @@
         <v>532.45140912225702</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>43650</v>
       </c>
@@ -3280,7 +3277,7 @@
         <v>617.54545330316398</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>43651</v>
       </c>
@@ -3294,7 +3291,7 @@
         <v>745.87846105338701</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>43652</v>
       </c>
@@ -3308,7 +3305,7 @@
         <v>826.16646017772598</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>43653</v>
       </c>
@@ -3322,7 +3319,7 @@
         <v>836.56541156931996</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>43654</v>
       </c>
@@ -3336,7 +3333,7 @@
         <v>297.06384758816199</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>43655</v>
       </c>
@@ -3350,7 +3347,7 @@
         <v>16.062493875464199</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>43656</v>
       </c>
@@ -3364,7 +3361,7 @@
         <v>323.08858812949302</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>43657</v>
       </c>
@@ -3387,29 +3384,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G430"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="27.88671875" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>622.63527302658804</v>
@@ -3422,9 +3419,9 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>357.11124363540699</v>
@@ -3437,9 +3434,9 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>402.82648326513402</v>
@@ -3452,9 +3449,9 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>855.14576858339694</v>
@@ -3467,9 +3464,9 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>295.755803790436</v>
@@ -3482,9 +3479,9 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>27.005112364037998</v>
@@ -3497,9 +3494,9 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>548.29328496125299</v>
@@ -3512,9 +3509,9 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>255.43824208905801</v>
@@ -3527,9 +3524,9 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>4.9173154075119498</v>
@@ -3542,9 +3539,9 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>82.920185581111795</v>
@@ -3557,9 +3554,9 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>756.08124563786305</v>
@@ -3572,9 +3569,9 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>81.006436943626994</v>
@@ -3587,9 +3584,9 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>384.44763286571401</v>
@@ -3602,9 +3599,9 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>806.80180181736398</v>
@@ -3617,9 +3614,9 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>545.14159381407603</v>
@@ -3632,9 +3629,9 @@
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>391.84648796520497</v>
@@ -3647,9 +3644,9 @@
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>542.91616878576497</v>
@@ -3662,9 +3659,9 @@
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>922.34047385398799</v>
@@ -3677,9 +3674,9 @@
       </c>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>626.54488188375399</v>
@@ -3692,9 +3689,9 @@
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>825.47934988827296</v>
@@ -3707,9 +3704,9 @@
       </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>336.18514642583301</v>
@@ -3722,9 +3719,9 @@
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>331.36054679690699</v>
@@ -3737,9 +3734,9 @@
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>6.1766442596090698</v>
@@ -3752,9 +3749,9 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>260.56022599008202</v>
@@ -3767,9 +3764,9 @@
       </c>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>616.03121585928</v>
@@ -3782,9 +3779,9 @@
       </c>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>389.59551379445099</v>
@@ -3797,9 +3794,9 @@
       </c>
       <c r="G27" s="3"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>464.68307993384298</v>
@@ -3812,9 +3809,9 @@
       </c>
       <c r="G28" s="3"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>213.009073771023</v>
@@ -3826,9 +3823,9 @@
         <v>491.53452049427102</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>527.23065409528397</v>
@@ -3840,9 +3837,9 @@
         <v>492.36057069266002</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>748.75360681913401</v>
@@ -3854,9 +3851,9 @@
         <v>238.74755362756599</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>773.17834413717503</v>
@@ -3868,9 +3865,9 @@
         <v>752.75460311184099</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>324.38388914853698</v>
@@ -3882,9 +3879,9 @@
         <v>159.03596216078901</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>727.99844676156295</v>
@@ -3896,9 +3893,9 @@
         <v>919.04830715513401</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>698.69310551931096</v>
@@ -3910,9 +3907,9 @@
         <v>905.781956795013</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>249.310594045637</v>
@@ -3924,9 +3921,9 @@
         <v>274.75568275238402</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>8.7157617758807397</v>
@@ -3938,9 +3935,9 @@
         <v>186.81132136043499</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>970.43701311945904</v>
@@ -3952,9 +3949,9 @@
         <v>27.712476521024598</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>720.06991923186501</v>
@@ -3966,9 +3963,9 @@
         <v>427.78848579433401</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>586.70266047731297</v>
@@ -3980,9 +3977,9 @@
         <v>160.34656422170701</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>275.97340101984599</v>
@@ -3994,9 +3991,9 @@
         <v>385.54512122288202</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>274.40838256727801</v>
@@ -4008,9 +4005,9 @@
         <v>919.851860468371</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43">
         <v>163.03375288142399</v>
@@ -4022,9 +4019,9 @@
         <v>663.64423230401906</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B44">
         <v>494.753054872093</v>
@@ -4036,9 +4033,9 @@
         <v>378.36491153645699</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B45">
         <v>955.51467436735902</v>
@@ -4050,9 +4047,9 @@
         <v>869.26688242783302</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B46">
         <v>726.27475198143497</v>
@@ -4064,9 +4061,9 @@
         <v>497.803769804002</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B47">
         <v>663.69996511439899</v>
@@ -4078,9 +4075,9 @@
         <v>14.581102277009</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B48">
         <v>506.84442801741801</v>
@@ -4092,9 +4089,9 @@
         <v>656.95718932268198</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B49">
         <v>623.16451693319902</v>
@@ -4106,9 +4103,9 @@
         <v>493.46431248713702</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B50">
         <v>38.008986329256601</v>
@@ -4120,9 +4117,9 @@
         <v>970.76624137780698</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51">
         <v>953.734240859686</v>
@@ -4134,9 +4131,9 @@
         <v>476.84423215214701</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B52">
         <v>619.49879909936897</v>
@@ -4148,9 +4145,9 @@
         <v>357.151885754658</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B53">
         <v>895.63920945568702</v>
@@ -4162,9 +4159,9 @@
         <v>171.77692246600901</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B54">
         <v>779.18605564040604</v>
@@ -4176,9 +4173,9 @@
         <v>788.05489434477795</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B55">
         <v>469.56050556041401</v>
@@ -4190,9 +4187,9 @@
         <v>331.96926207116502</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56">
         <v>392.60731867539602</v>
@@ -4204,9 +4201,9 @@
         <v>173.90368162117201</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B57">
         <v>336.26024772534402</v>
@@ -4218,9 +4215,9 @@
         <v>451.07815135255203</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58">
         <v>67.426879479474294</v>
@@ -4232,9 +4229,9 @@
         <v>668.95641140540795</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B59">
         <v>5.7577819086009896</v>
@@ -4246,9 +4243,9 @@
         <v>84.093624181559903</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B60">
         <v>161.43674117840499</v>
@@ -4260,9 +4257,9 @@
         <v>607.668413358571</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61">
         <v>982.05236419086805</v>
@@ -4274,9 +4271,9 @@
         <v>966.08798764349797</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B62">
         <v>938.56152484273298</v>
@@ -4288,9 +4285,9 @@
         <v>719.28460797269395</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B63">
         <v>37.053330543237102</v>
@@ -4302,9 +4299,9 @@
         <v>171.710419754188</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B64">
         <v>769.04778135863296</v>
@@ -4316,9 +4313,9 @@
         <v>266.14264413847098</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B65">
         <v>365.79048225739302</v>
@@ -4330,9 +4327,9 @@
         <v>886.47663708758296</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66">
         <v>772.36744500965096</v>
@@ -4344,9 +4341,9 @@
         <v>834.37324110544603</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B67">
         <v>630.16040035257004</v>
@@ -4358,9 +4355,9 @@
         <v>558.38469263753996</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68">
         <v>507.274950358306</v>
@@ -4372,9 +4369,9 @@
         <v>775.27408346183904</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B69">
         <v>908.15299548178098</v>
@@ -4386,9 +4383,9 @@
         <v>107.219809664896</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B70">
         <v>485.23922057348301</v>
@@ -4400,9 +4397,9 @@
         <v>455.09820397063299</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B71">
         <v>975.89805330544698</v>
@@ -4414,9 +4411,9 @@
         <v>366.47771770807901</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B72">
         <v>272.26219011343898</v>
@@ -4428,9 +4425,9 @@
         <v>359.98674668343602</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B73">
         <v>293.51322138987001</v>
@@ -4442,9 +4439,9 @@
         <v>661.61266246678895</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B74">
         <v>646.30120310580105</v>
@@ -4456,9 +4453,9 @@
         <v>254.11599880604601</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B75">
         <v>327.81161793896899</v>
@@ -4470,9 +4467,9 @@
         <v>372.65058582898001</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B76">
         <v>68.7618293023164</v>
@@ -4484,9 +4481,9 @@
         <v>626.631544993028</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B77">
         <v>57.927746286743101</v>
@@ -4498,9 +4495,9 @@
         <v>499.37280344616403</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B78">
         <v>408.56540339177599</v>
@@ -4512,9 +4509,9 @@
         <v>808.92417547761897</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B79">
         <v>284.75347258176203</v>
@@ -4526,9 +4523,9 @@
         <v>481.69326576279798</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B80">
         <v>477.614644833277</v>
@@ -4540,9 +4537,9 @@
         <v>823.94155218105902</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B81">
         <v>792.95879565705297</v>
@@ -4554,9 +4551,9 @@
         <v>566.25639527464898</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B82">
         <v>159.02915452468599</v>
@@ -4568,9 +4565,9 @@
         <v>374.68996670068901</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B83">
         <v>729.93428660680297</v>
@@ -4582,9 +4579,9 @@
         <v>76.77833447626</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B84">
         <v>993.91558600836095</v>
@@ -4596,9 +4593,9 @@
         <v>479.642459003044</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85">
         <v>909.06529474874503</v>
@@ -4610,9 +4607,9 @@
         <v>992.67697467261496</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B86">
         <v>874.64628900329899</v>
@@ -4624,9 +4621,9 @@
         <v>268.30286662535201</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B87">
         <v>644.13572162344303</v>
@@ -4638,9 +4635,9 @@
         <v>657.77096986649599</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B88">
         <v>286.73416032513097</v>
@@ -4652,9 +4649,9 @@
         <v>638.60534477136696</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B89">
         <v>412.29230066852</v>
@@ -4666,9 +4663,9 @@
         <v>626.66533880698398</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B90">
         <v>273.11058329475202</v>
@@ -4680,9 +4677,9 @@
         <v>491.707643251452</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91">
         <v>880.49789976724696</v>
@@ -4694,9 +4691,9 @@
         <v>709.12184310558098</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B92">
         <v>684.13280663663397</v>
@@ -4708,9 +4705,9 @@
         <v>206.356417955333</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B93">
         <v>677.35955579264805</v>
@@ -4722,9 +4719,9 @@
         <v>346.572654546401</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B94">
         <v>190.63635378031299</v>
@@ -4736,9 +4733,9 @@
         <v>596.63839478727402</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B95">
         <v>452.93344231351199</v>
@@ -4750,9 +4747,9 @@
         <v>979.88897480756805</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B96">
         <v>450.50630434753703</v>
@@ -4764,9 +4761,9 @@
         <v>701.828120202538</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B97">
         <v>70.258639065389104</v>
@@ -4778,9 +4775,9 @@
         <v>827.45275065704595</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B98">
         <v>147.40416282720099</v>
@@ -4792,9 +4789,9 @@
         <v>522.65424952124295</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B99">
         <v>862.42826598031695</v>
@@ -4806,9 +4803,9 @@
         <v>62.836406853972001</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B100">
         <v>178.661930019149</v>
@@ -4820,9 +4817,9 @@
         <v>500.34284136658698</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B101">
         <v>451.122401281929</v>
@@ -4834,9 +4831,9 @@
         <v>722.91061927697103</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B102">
         <v>17.000230846413199</v>
@@ -4848,9 +4845,9 @@
         <v>381.54072654317002</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B103">
         <v>536.09567553394004</v>
@@ -4862,9 +4859,9 @@
         <v>66.538510162966006</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B104">
         <v>614.36290413091001</v>
@@ -4876,9 +4873,9 @@
         <v>627.212274267064</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B105">
         <v>891.80475130509797</v>
@@ -4890,9 +4887,9 @@
         <v>968.20176978953305</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B106">
         <v>497.04762614246999</v>
@@ -4904,9 +4901,9 @@
         <v>363.57828073761198</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B107">
         <v>678.59971451900799</v>
@@ -4918,9 +4915,9 @@
         <v>932.05396036202205</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B108">
         <v>181.02053819658201</v>
@@ -4932,9 +4929,9 @@
         <v>463.07797769859201</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B109">
         <v>417.22158920111502</v>
@@ -4946,9 +4943,9 @@
         <v>915.53540348027002</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B110">
         <v>791.46409288255302</v>
@@ -4960,9 +4957,9 @@
         <v>341.31908780456899</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B111">
         <v>836.97295833114595</v>
@@ -4974,9 +4971,9 @@
         <v>413.53504742672101</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B112">
         <v>570.375418764085</v>
@@ -4988,9 +4985,9 @@
         <v>763.44667501197603</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B113">
         <v>705.88593267080705</v>
@@ -5002,9 +4999,9 @@
         <v>888.23234739898805</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B114">
         <v>232.97325196808001</v>
@@ -5016,9 +5013,9 @@
         <v>50.508893194650099</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B115">
         <v>374.08537880106701</v>
@@ -5030,9 +5027,9 @@
         <v>638.02729401671195</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B116">
         <v>534.55536437093895</v>
@@ -5044,9 +5041,9 @@
         <v>492.69451955309103</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B117">
         <v>399.172179164608</v>
@@ -5058,9 +5055,9 @@
         <v>570.78231439589797</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B118">
         <v>437.18899543142498</v>
@@ -5072,9 +5069,9 @@
         <v>363.18105035024399</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B119">
         <v>633.43814636175</v>
@@ -5086,9 +5083,9 @@
         <v>752.08749222093502</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B120">
         <v>4.1196805580615603</v>
@@ -5100,9 +5097,9 @@
         <v>827.71703700998398</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B121">
         <v>893.73555187900399</v>
@@ -5114,9 +5111,9 @@
         <v>989.909574844281</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B122">
         <v>870.75064309185097</v>
@@ -5128,9 +5125,9 @@
         <v>791.86318478594205</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B123">
         <v>699.65175955704501</v>
@@ -5142,9 +5139,9 @@
         <v>282.698231137108</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B124">
         <v>607.71888317169305</v>
@@ -5156,9 +5153,9 @@
         <v>716.33481277161798</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B125">
         <v>597.20597991348905</v>
@@ -5170,9 +5167,9 @@
         <v>569.40768535369796</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B126">
         <v>687.45250361595504</v>
@@ -5184,9 +5181,9 @@
         <v>80.987927586822494</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B127">
         <v>989.09047682218795</v>
@@ -5198,9 +5195,9 @@
         <v>23.429076176010401</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B128">
         <v>633.42530854973097</v>
@@ -5212,9 +5209,9 @@
         <v>313.57756184247501</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B129">
         <v>878.73174615158598</v>
@@ -5226,9 +5223,9 @@
         <v>323.03430114485201</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B130">
         <v>109.660879617795</v>
@@ -5240,9 +5237,9 @@
         <v>716.917844011792</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B131">
         <v>977.52903755448403</v>
@@ -5254,9 +5251,9 @@
         <v>418.48376504300199</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B132">
         <v>128.157731589436</v>
@@ -5268,9 +5265,9 @@
         <v>313.20317472355202</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B133">
         <v>833.76331331157201</v>
@@ -5282,9 +5279,9 @@
         <v>234.418897200418</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B134">
         <v>821.31650442520504</v>
@@ -5296,9 +5293,9 @@
         <v>362.54647730766698</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B135">
         <v>527.14586348342903</v>
@@ -5310,9 +5307,9 @@
         <v>779.80729227562199</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B136">
         <v>31.570458144455799</v>
@@ -5324,9 +5321,9 @@
         <v>516.90089866840594</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B137">
         <v>57.556308399825397</v>
@@ -5338,9 +5335,9 @@
         <v>408.10836557876399</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B138">
         <v>136.41194285437101</v>
@@ -5352,9 +5349,9 @@
         <v>870.55952769914597</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B139">
         <v>426.85139189833802</v>
@@ -5366,9 +5363,9 @@
         <v>549.00682129299003</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B140">
         <v>182.49235803931501</v>
@@ -5380,9 +5377,9 @@
         <v>401.82545659092602</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B141">
         <v>975.17300533441198</v>
@@ -5394,9 +5391,9 @@
         <v>748.99674997466195</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B142">
         <v>884.74964198710597</v>
@@ -5408,9 +5405,9 @@
         <v>604.56254075502898</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B143">
         <v>885.27383216596502</v>
@@ -5422,9 +5419,9 @@
         <v>63.386122280306701</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B144">
         <v>739.55950558278005</v>
@@ -5436,9 +5433,9 @@
         <v>472.56446712331098</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B145">
         <v>465.40139629024901</v>
@@ -5450,9 +5447,9 @@
         <v>669.98636241704503</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B146">
         <v>410.21506673031797</v>
@@ -5464,9 +5461,9 @@
         <v>71.127707591098698</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B147">
         <v>977.41710225377005</v>
@@ -5478,9 +5475,9 @@
         <v>486.68974565041202</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B148">
         <v>648.015194495022</v>
@@ -5492,9 +5489,9 @@
         <v>694.64355969625899</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B149">
         <v>486.68418016359198</v>
@@ -5506,9 +5503,9 @@
         <v>620.64277499279603</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B150">
         <v>599.54692877238301</v>
@@ -5520,9 +5517,9 @@
         <v>79.947163770393203</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B151">
         <v>101.935972085354</v>
@@ -5534,9 +5531,9 @@
         <v>441.45967458359797</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B152">
         <v>56.629387664373802</v>
@@ -5548,9 +5545,9 @@
         <v>161.11980993628899</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B153">
         <v>985.07537643575597</v>
@@ -5562,9 +5559,9 @@
         <v>408.45949220784303</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B154">
         <v>780.95443353487804</v>
@@ -5576,9 +5573,9 @@
         <v>194.362671629261</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B155">
         <v>990.46901265832105</v>
@@ -5590,9 +5587,9 @@
         <v>292.336274063465</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B156">
         <v>712.05918886880295</v>
@@ -5604,9 +5601,9 @@
         <v>693.19189158772394</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B157">
         <v>492.52425596040598</v>
@@ -5618,9 +5615,9 @@
         <v>545.38083795902105</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B158">
         <v>683.37440256582499</v>
@@ -5632,9 +5629,9 @@
         <v>76.650061316583404</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B159">
         <v>539.31751149989304</v>
@@ -5646,9 +5643,9 @@
         <v>320.82582080204799</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B160">
         <v>641.06512036438096</v>
@@ -5660,9 +5657,9 @@
         <v>343.88340789865299</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B161">
         <v>307.32089531627702</v>
@@ -5674,9 +5671,9 @@
         <v>859.46428552389898</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B162">
         <v>876.59309556932897</v>
@@ -5688,9 +5685,9 @@
         <v>22.851215451327999</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B163">
         <v>383.32034414923999</v>
@@ -5702,9 +5699,9 @@
         <v>823.97192887257302</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B164">
         <v>488.74281801592798</v>
@@ -5716,9 +5713,9 @@
         <v>742.33771206471795</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B165">
         <v>255.092436650602</v>
@@ -5730,9 +5727,9 @@
         <v>114.94239318124301</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B166">
         <v>661.43484814420799</v>
@@ -5744,9 +5741,9 @@
         <v>318.60553715449402</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B167">
         <v>2.93412357068634</v>
@@ -5758,9 +5755,9 @@
         <v>175.89770027051199</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B168">
         <v>451.48395989059799</v>
@@ -5772,9 +5769,9 @@
         <v>104.752036141017</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B169">
         <v>483.19803677012101</v>
@@ -5786,9 +5783,9 @@
         <v>363.08090291274402</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B170">
         <v>568.75595621609705</v>
@@ -5800,9 +5797,9 @@
         <v>726.85857740274696</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B171">
         <v>207.41813736208201</v>
@@ -5814,9 +5811,9 @@
         <v>751.99471199326695</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B172">
         <v>871.14902963004704</v>
@@ -5828,9 +5825,9 @@
         <v>932.80129341095198</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B173">
         <v>858.01809606646498</v>
@@ -5842,9 +5839,9 @@
         <v>115.736025306949</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B174">
         <v>999.06005576849896</v>
@@ -5856,9 +5853,9 @@
         <v>871.87838625448501</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B175">
         <v>819.26409035072595</v>
@@ -5870,9 +5867,9 @@
         <v>884.62290138913102</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B176">
         <v>354.65370749891503</v>
@@ -5884,9 +5881,9 @@
         <v>792.93703901896697</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B177">
         <v>493.07213221102899</v>
@@ -5898,9 +5895,9 @@
         <v>661.04668215567995</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B178">
         <v>508.40886212107102</v>
@@ -5912,9 +5909,9 @@
         <v>531.585141918678</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B179">
         <v>966.47889319362196</v>
@@ -5926,9 +5923,9 @@
         <v>332.28529044608302</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B180">
         <v>774.09648169778598</v>
@@ -5940,9 +5937,9 @@
         <v>615.78115790941195</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B181">
         <v>110.96607638866401</v>
@@ -5954,9 +5951,9 @@
         <v>436.11378527982203</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B182">
         <v>779.258846440703</v>
@@ -5968,9 +5965,9 @@
         <v>264.53380304771099</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B183">
         <v>375.08770082109203</v>
@@ -5982,9 +5979,9 @@
         <v>420.02974231289602</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B184">
         <v>522.150990659272</v>
@@ -5996,9 +5993,9 @@
         <v>123.85378353916001</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B185">
         <v>404.29058686962202</v>
@@ -6010,9 +6007,9 @@
         <v>686.91492867926195</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B186">
         <v>865.33848670794202</v>
@@ -6024,9 +6021,9 @@
         <v>868.36886645531501</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B187">
         <v>928.37353146734904</v>
@@ -6038,9 +6035,9 @@
         <v>467.385983923156</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B188">
         <v>630.07557139084997</v>
@@ -6052,9 +6049,9 @@
         <v>801.81196180443396</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B189">
         <v>270.204409920888</v>
@@ -6066,9 +6063,9 @@
         <v>495.46723476266698</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B190">
         <v>486.60788866261902</v>
@@ -6080,9 +6077,9 @@
         <v>721.58479680298899</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B191">
         <v>233.50451025269399</v>
@@ -6094,9 +6091,9 @@
         <v>138.190877414645</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B192">
         <v>128.90334015178101</v>
@@ -6108,9 +6105,9 @@
         <v>672.70527476931795</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B193">
         <v>565.31317672989405</v>
@@ -6122,9 +6119,9 @@
         <v>743.54839659353502</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B194">
         <v>635.39681641210996</v>
@@ -6136,9 +6133,9 @@
         <v>239.25727168451601</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B195">
         <v>287.07532086861102</v>
@@ -6150,9 +6147,9 @@
         <v>920.94221362015605</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B196">
         <v>842.21200875817101</v>
@@ -6164,9 +6161,9 @@
         <v>311.35477361819397</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B197">
         <v>253.77824606538701</v>
@@ -6178,9 +6175,9 @@
         <v>296.04627847182797</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B198">
         <v>605.66027063827903</v>
@@ -6192,9 +6189,9 @@
         <v>2.6458882697988302</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B199">
         <v>513.20772098825296</v>
@@ -6206,9 +6203,9 @@
         <v>180.53312124322099</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B200">
         <v>18.287237103408899</v>
@@ -6220,9 +6217,9 @@
         <v>779.890158738644</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B201">
         <v>717.14106006681402</v>
@@ -6234,9 +6231,9 @@
         <v>256.36296396840498</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B202">
         <v>797.58334399437695</v>
@@ -6248,9 +6245,9 @@
         <v>617.69117529814105</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B203">
         <v>268.73268641627902</v>
@@ -6262,9 +6259,9 @@
         <v>202.597806804508</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B204">
         <v>259.11318197382298</v>
@@ -6276,9 +6273,9 @@
         <v>787.579130627994</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B205">
         <v>677.54995591337502</v>
@@ -6290,9 +6287,9 @@
         <v>136.03505921237101</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B206">
         <v>724.21647119602301</v>
@@ -6304,9 +6301,9 @@
         <v>220.94883662066599</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B207">
         <v>918.81551172352101</v>
@@ -6318,9 +6315,9 @@
         <v>204.74066590885801</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B208">
         <v>518.52844377419001</v>
@@ -6332,9 +6329,9 @@
         <v>693.181046559327</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B209">
         <v>552.37703422285904</v>
@@ -6346,9 +6343,9 @@
         <v>803.05416983155101</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B210">
         <v>679.05038717920502</v>
@@ -6360,9 +6357,9 @@
         <v>671.02533523759598</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B211">
         <v>292.288422187788</v>
@@ -6374,9 +6371,9 @@
         <v>589.91060554076796</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B212">
         <v>639.86472586955995</v>
@@ -6388,9 +6385,9 @@
         <v>49.356827244780398</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B213">
         <v>141.850535465565</v>
@@ -6402,9 +6399,9 @@
         <v>685.98509453935196</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B214">
         <v>834.03736394722796</v>
@@ -6416,9 +6413,9 @@
         <v>554.73079515787504</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B215">
         <v>576.66770505722604</v>
@@ -6430,9 +6427,9 @@
         <v>490.24781929724799</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B216">
         <v>107.02951945313301</v>
@@ -6444,9 +6441,9 @@
         <v>436.48801208537401</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B217">
         <v>293.25019370111801</v>
@@ -6458,9 +6455,9 @@
         <v>727.46365633302298</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B218">
         <v>145.65915770400099</v>
@@ -6472,9 +6469,9 @@
         <v>378.06732545773599</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B219">
         <v>515.50705218494397</v>
@@ -6486,9 +6483,9 @@
         <v>470.25601657168301</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B220">
         <v>107.206761352689</v>
@@ -6500,9 +6497,9 @@
         <v>298.57367455783202</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B221">
         <v>202.110550240582</v>
@@ -6514,9 +6511,9 @@
         <v>597.56748919720906</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B222">
         <v>285.54802436911098</v>
@@ -6528,9 +6525,9 @@
         <v>146.19285804664099</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B223">
         <v>632.83335117337401</v>
@@ -6542,9 +6539,9 @@
         <v>619.10298990649403</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B224">
         <v>803.46168392686695</v>
@@ -6556,9 +6553,9 @@
         <v>564.32729965973897</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B225">
         <v>285.35802638373298</v>
@@ -6570,9 +6567,9 @@
         <v>13.796321950675599</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B226">
         <v>352.078284827294</v>
@@ -6584,9 +6581,9 @@
         <v>22.374569060844301</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B227">
         <v>741.230998617762</v>
@@ -6598,9 +6595,9 @@
         <v>767.44269136581397</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B228">
         <v>615.22717455958002</v>
@@ -6612,9 +6609,9 @@
         <v>401.85584571677998</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B229">
         <v>355.63209010620898</v>
@@ -6626,9 +6623,9 @@
         <v>809.86130019271002</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B230">
         <v>855.11839792817602</v>
@@ -6640,9 +6637,9 @@
         <v>144.692016903492</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B231">
         <v>203.96353586689199</v>
@@ -6654,9 +6651,9 @@
         <v>374.290368662996</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B232">
         <v>399.73712590985701</v>
@@ -6668,9 +6665,9 @@
         <v>278.32257293363898</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B233">
         <v>455.18321719720399</v>
@@ -6682,9 +6679,9 @@
         <v>941.90952692464202</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B234">
         <v>525.04151700764703</v>
@@ -6696,9 +6693,9 @@
         <v>461.68911871944402</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B235">
         <v>484.24845174350003</v>
@@ -6710,9 +6707,9 @@
         <v>488.23792902711801</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B236">
         <v>861.40978915051699</v>
@@ -6724,9 +6721,9 @@
         <v>945.69042418881702</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B237">
         <v>95.332278571085794</v>
@@ -6738,9 +6735,9 @@
         <v>849.77624461235098</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B238">
         <v>790.621466874004</v>
@@ -6752,9 +6749,9 @@
         <v>420.26399183798497</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B239">
         <v>646.059525226304</v>
@@ -6766,9 +6763,9 @@
         <v>557.41007151668396</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B240">
         <v>500.128904704077</v>
@@ -6780,9 +6777,9 @@
         <v>499.88767712604601</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B241">
         <v>437.027965052897</v>
@@ -6794,9 +6791,9 @@
         <v>683.66226073946098</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B242">
         <v>906.43947869370504</v>
@@ -6808,9 +6805,9 @@
         <v>313.20485113146299</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B243">
         <v>376.781033145771</v>
@@ -6822,9 +6819,9 @@
         <v>73.718746829063406</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B244">
         <v>509.02662393763802</v>
@@ -6836,9 +6833,9 @@
         <v>643.410992725136</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A245" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B245">
         <v>315.01770455314499</v>
@@ -6850,9 +6847,9 @@
         <v>164.772341500441</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B246">
         <v>454.754096462512</v>
@@ -6864,9 +6861,9 @@
         <v>662.76255597173895</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B247">
         <v>297.59622462428001</v>
@@ -6878,9 +6875,9 @@
         <v>659.39090625129302</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B248">
         <v>765.88331578401596</v>
@@ -6892,9 +6889,9 @@
         <v>497.37525742196698</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B249">
         <v>595.92685927782895</v>
@@ -6906,9 +6903,9 @@
         <v>18.8206809246775</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B250">
         <v>740.32721573458696</v>
@@ -6920,9 +6917,9 @@
         <v>89.813111615543505</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B251">
         <v>146.772544302835</v>
@@ -6934,9 +6931,9 @@
         <v>922.54721754604395</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B252">
         <v>727.99278775999096</v>
@@ -6948,9 +6945,9 @@
         <v>28.737247502678301</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B253">
         <v>27.319087334976999</v>
@@ -6962,9 +6959,9 @@
         <v>916.836387473336</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B254">
         <v>142.35432906012301</v>
@@ -6976,9 +6973,9 @@
         <v>695.37252714148804</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B255">
         <v>902.54373122849097</v>
@@ -6990,9 +6987,9 @@
         <v>240.488577975428</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B256">
         <v>335.03329546061701</v>
@@ -7004,9 +7001,9 @@
         <v>184.757633258087</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B257">
         <v>382.314495744716</v>
@@ -7018,9 +7015,9 @@
         <v>223.52851554195399</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B258">
         <v>948.80816148890096</v>
@@ -7032,9 +7029,9 @@
         <v>967.69780487166099</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B259">
         <v>782.85230092945005</v>
@@ -7046,9 +7043,9 @@
         <v>698.916057348957</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B260">
         <v>144.934129067405</v>
@@ -7060,9 +7057,9 @@
         <v>776.20097859882503</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B261">
         <v>978.30352495042996</v>
@@ -7074,9 +7071,9 @@
         <v>785.61984182920503</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A262" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B262">
         <v>103.24846972168</v>
@@ -7088,9 +7085,9 @@
         <v>437.800541225774</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B263">
         <v>990.81099018425903</v>
@@ -7102,9 +7099,9 @@
         <v>206.816065141933</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B264">
         <v>758.766734735348</v>
@@ -7116,9 +7113,9 @@
         <v>615.98911279693095</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B265">
         <v>208.20731400275</v>
@@ -7130,9 +7127,9 @@
         <v>1.35600473336917</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B266">
         <v>190.46326801440301</v>
@@ -7144,9 +7141,9 @@
         <v>56.127044145654502</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B267">
         <v>440.29551996320203</v>
@@ -7158,9 +7155,9 @@
         <v>269.93454522132998</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B268">
         <v>545.52625063902599</v>
@@ -7172,9 +7169,9 @@
         <v>741.415344630665</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B269">
         <v>818.11495685770797</v>
@@ -7186,9 +7183,9 @@
         <v>458.50046509744999</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B270">
         <v>238.00101449529899</v>
@@ -7200,9 +7197,9 @@
         <v>481.79281402130601</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A271" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B271">
         <v>883.05204276617405</v>
@@ -7214,9 +7211,9 @@
         <v>433.19486062010702</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B272">
         <v>656.14999504932405</v>
@@ -7228,9 +7225,9 @@
         <v>639.94708169009095</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B273">
         <v>799.25909991396998</v>
@@ -7242,9 +7239,9 @@
         <v>126.30616474714201</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B274">
         <v>309.95958223975902</v>
@@ -7256,9 +7253,9 @@
         <v>267.34745642099398</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B275">
         <v>971.32799324622704</v>
@@ -7270,9 +7267,9 @@
         <v>299.926556864536</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B276">
         <v>844.51756615949603</v>
@@ -7284,9 +7281,9 @@
         <v>169.336492742422</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B277">
         <v>776.15378067859399</v>
@@ -7298,9 +7295,9 @@
         <v>104.53596140531</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A278" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B278">
         <v>987.53638695691996</v>
@@ -7312,9 +7309,9 @@
         <v>311.16536463535198</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B279">
         <v>823.76675718666104</v>
@@ -7326,9 +7323,9 @@
         <v>791.47644317251297</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B280">
         <v>919.28510080925503</v>
@@ -7340,9 +7337,9 @@
         <v>613.49535324154203</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B281">
         <v>227.90314009332701</v>
@@ -7354,9 +7351,9 @@
         <v>967.72082149538301</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A282" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B282">
         <v>378.68955759548999</v>
@@ -7368,9 +7365,9 @@
         <v>202.013411875282</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B283">
         <v>778.89685500551195</v>
@@ -7382,9 +7379,9 @@
         <v>740.72963291396297</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B284">
         <v>675.29880620090705</v>
@@ -7396,9 +7393,9 @@
         <v>877.70261980979205</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B285">
         <v>49.425009841692201</v>
@@ -7410,9 +7407,9 @@
         <v>75.400096592313105</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B286">
         <v>421.065418759088</v>
@@ -7424,9 +7421,9 @@
         <v>594.36783391003803</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B287">
         <v>583.92675505511602</v>
@@ -7438,9 +7435,9 @@
         <v>749.02043060642097</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A288" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B288">
         <v>369.760441837678</v>
@@ -7452,9 +7449,9 @@
         <v>827.15986419499905</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B289">
         <v>691.56234524839897</v>
@@ -7466,9 +7463,9 @@
         <v>931.411782205642</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A290" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B290">
         <v>119.737171279764</v>
@@ -7480,9 +7477,9 @@
         <v>550.60796291951897</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B291">
         <v>947.12410900892098</v>
@@ -7494,9 +7491,9 @@
         <v>518.12953918381402</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B292">
         <v>627.71153673995502</v>
@@ -7508,9 +7505,9 @@
         <v>668.64787898179895</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B293">
         <v>439.79024140251499</v>
@@ -7522,9 +7519,9 @@
         <v>321.13231162987501</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A294" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B294">
         <v>631.249616875019</v>
@@ -7536,9 +7533,9 @@
         <v>841.88681760801001</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B295">
         <v>227.689896184476</v>
@@ -7550,9 +7547,9 @@
         <v>971.709925163619</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B296">
         <v>650.75014176788102</v>
@@ -7564,9 +7561,9 @@
         <v>55.182423620730603</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B297">
         <v>331.08334221909502</v>
@@ -7578,9 +7575,9 @@
         <v>165.47218711585799</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A298" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B298">
         <v>372.581245650185</v>
@@ -7592,9 +7589,9 @@
         <v>431.48143020429097</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B299">
         <v>655.91222981829299</v>
@@ -7606,9 +7603,9 @@
         <v>623.71337756177002</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B300">
         <v>531.63764660442905</v>
@@ -7620,9 +7617,9 @@
         <v>12.4308125133185</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A301" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B301">
         <v>413.09394979443999</v>
@@ -7634,9 +7631,9 @@
         <v>453.17060702011401</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A302" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B302">
         <v>394.94035968502902</v>
@@ -7648,9 +7645,9 @@
         <v>633.80515060073196</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A303" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B303">
         <v>273.291531339936</v>
@@ -7662,9 +7659,9 @@
         <v>899.39689388188697</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A304" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B304">
         <v>678.93798072201298</v>
@@ -7676,9 +7673,9 @@
         <v>841.39769927216696</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A305" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B305">
         <v>834.35651647490897</v>
@@ -7690,9 +7687,9 @@
         <v>524.88811145216096</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A306" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B306">
         <v>890.96118609696998</v>
@@ -7704,9 +7701,9 @@
         <v>995.17225747448595</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A307" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B307">
         <v>324.360711592185</v>
@@ -7718,9 +7715,9 @@
         <v>423.33904089640203</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A308" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B308">
         <v>570.10666468475301</v>
@@ -7732,9 +7729,9 @@
         <v>346.06243315987302</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A309" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B309">
         <v>993.84712940920701</v>
@@ -7746,9 +7743,9 @@
         <v>903.79882575242095</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A310" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B310">
         <v>919.06327843428699</v>
@@ -7760,9 +7757,9 @@
         <v>517.54460718547</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A311" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B311">
         <v>371.75579475107799</v>
@@ -7774,9 +7771,9 @@
         <v>200.490028184306</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A312" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B312">
         <v>731.455231961506</v>
@@ -7788,9 +7785,9 @@
         <v>514.29629380476604</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A313" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B313">
         <v>760.12960018399394</v>
@@ -7802,9 +7799,9 @@
         <v>28.701692390781801</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A314" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B314">
         <v>989.47219397262802</v>
@@ -7816,9 +7813,9 @@
         <v>479.84828031064001</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A315" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B315">
         <v>883.88281579178397</v>
@@ -7830,9 +7827,9 @@
         <v>207.481129975236</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A316" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B316">
         <v>399.35827237472301</v>
@@ -7844,9 +7841,9 @@
         <v>455.82572443849398</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A317" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B317">
         <v>586.31101176669097</v>
@@ -7858,9 +7855,9 @@
         <v>446.52920776455699</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A318" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B318">
         <v>466.90500791782603</v>
@@ -7872,9 +7869,9 @@
         <v>663.02879623824799</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A319" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B319">
         <v>625.73728554186198</v>
@@ -7886,9 +7883,9 @@
         <v>814.02123831562994</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A320" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B320">
         <v>304.844602528466</v>
@@ -7900,9 +7897,9 @@
         <v>344.40275528508698</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A321" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B321">
         <v>418.88633713260401</v>
@@ -7914,9 +7911,9 @@
         <v>472.42612756056701</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A322" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B322">
         <v>699.57310704765496</v>
@@ -7928,9 +7925,9 @@
         <v>819.899054327302</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A323" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B323">
         <v>646.85258143277395</v>
@@ -7942,9 +7939,9 @@
         <v>824.91320953738</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A324" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B324">
         <v>226.229792145875</v>
@@ -7956,9 +7953,9 @@
         <v>698.40387686399197</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A325" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B325">
         <v>505.36248393736599</v>
@@ -7970,9 +7967,9 @@
         <v>364.267735678245</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A326" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B326">
         <v>999.92104873420101</v>
@@ -7984,9 +7981,9 @@
         <v>705.07422279475497</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A327" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B327">
         <v>119.163440512622</v>
@@ -7998,9 +7995,9 @@
         <v>840.002820224831</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A328" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B328">
         <v>787.12344477539</v>
@@ -8012,9 +8009,9 @@
         <v>377.89549532043497</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A329" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B329">
         <v>533.30296275665296</v>
@@ -8026,9 +8023,9 @@
         <v>413.86012598989203</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A330" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B330">
         <v>8.8656642336362204</v>
@@ -8040,9 +8037,9 @@
         <v>588.24898185869802</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A331" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B331">
         <v>329.182635481131</v>
@@ -8054,9 +8051,9 @@
         <v>832.769479984094</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A332" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B332">
         <v>0.14266432148712899</v>
@@ -8068,9 +8065,9 @@
         <v>578.77238094891004</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A333" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B333">
         <v>193.83756448817201</v>
@@ -8082,9 +8079,9 @@
         <v>19.544608198967101</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A334" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B334">
         <v>151.719367083571</v>
@@ -8096,9 +8093,9 @@
         <v>768.27242376122899</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A335" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B335">
         <v>341.15708062609099</v>
@@ -8110,9 +8107,9 @@
         <v>734.85811595993505</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A336" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B336">
         <v>404.98373262027502</v>
@@ -8124,9 +8121,9 @@
         <v>324.32778661089401</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A337" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B337">
         <v>149.955685578203</v>
@@ -8138,9 +8135,9 @@
         <v>833.79472085485304</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A338" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B338">
         <v>757.87392703148703</v>
@@ -8152,9 +8149,9 @@
         <v>415.84820831147499</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A339" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B339">
         <v>464.11033377842301</v>
@@ -8166,9 +8163,9 @@
         <v>779.45972053634898</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A340" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B340">
         <v>754.21145963312301</v>
@@ -8180,9 +8177,9 @@
         <v>118.667913048868</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A341" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B341">
         <v>267.66357873447299</v>
@@ -8194,9 +8191,9 @@
         <v>869.44296911494303</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A342" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B342">
         <v>983.83704005774905</v>
@@ -8208,9 +8205,9 @@
         <v>67.845801601339303</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A343" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B343">
         <v>278.12927968950402</v>
@@ -8222,9 +8219,9 @@
         <v>582.523480648646</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A344" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B344">
         <v>55.681302535775203</v>
@@ -8236,9 +8233,9 @@
         <v>50.217693007518399</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A345" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B345">
         <v>675.89820106750597</v>
@@ -8250,9 +8247,9 @@
         <v>601.72810105197402</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A346" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B346">
         <v>994.74838158628495</v>
@@ -8264,9 +8261,9 @@
         <v>129.29278130818</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A347" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B347">
         <v>379.58110298248499</v>
@@ -8278,9 +8275,9 @@
         <v>19.189719808307601</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A348" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B348">
         <v>934.61085130322294</v>
@@ -8292,9 +8289,9 @@
         <v>919.42372637731501</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A349" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B349">
         <v>491.17629079614699</v>
@@ -8306,9 +8303,9 @@
         <v>752.69025025157896</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A350" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B350">
         <v>741.24073100275496</v>
@@ -8320,9 +8317,9 @@
         <v>931.28481557250404</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A351" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B351">
         <v>568.37815143338503</v>
@@ -8334,9 +8331,9 @@
         <v>152.99479001871401</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A352" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B352">
         <v>798.12739298174699</v>
@@ -8348,9 +8345,9 @@
         <v>934.76440376104904</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A353" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B353">
         <v>233.33499550622</v>
@@ -8362,9 +8359,9 @@
         <v>136.402991996314</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A354" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B354">
         <v>57.9386417485415</v>
@@ -8376,9 +8373,9 @@
         <v>618.69819987257495</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A355" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B355">
         <v>412.07221880652997</v>
@@ -8390,9 +8387,9 @@
         <v>78.426320609023406</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A356" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B356">
         <v>960.46624969797597</v>
@@ -8404,9 +8401,9 @@
         <v>582.64182935927295</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A357" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B357">
         <v>120.05461306822799</v>
@@ -8418,9 +8415,9 @@
         <v>747.62167646974694</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A358" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B358">
         <v>491.28592963786599</v>
@@ -8432,9 +8429,9 @@
         <v>475.56905191314598</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A359" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B359">
         <v>347.69970119948903</v>
@@ -8446,9 +8443,9 @@
         <v>220.79593328249399</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A360" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B360">
         <v>686.60984643452105</v>
@@ -8460,9 +8457,9 @@
         <v>266.30997004256301</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A361" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B361">
         <v>33.9717283124753</v>
@@ -8474,9 +8471,9 @@
         <v>695.508814147066</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A362" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B362">
         <v>512.46050508634005</v>
@@ -8488,9 +8485,9 @@
         <v>965.95970570888699</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A363" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B363">
         <v>589.21643916600601</v>
@@ -8502,9 +8499,9 @@
         <v>691.77097725466297</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A364" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B364">
         <v>914.20277096530299</v>
@@ -8516,9 +8513,9 @@
         <v>730.07210998901098</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A365" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B365">
         <v>800.63720903174897</v>
@@ -8530,9 +8527,9 @@
         <v>790.55760126685402</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A366" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B366">
         <v>535.12140732110902</v>
@@ -8544,9 +8541,9 @@
         <v>114.124196634885</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A367" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B367">
         <v>490.57058715586197</v>
@@ -8558,9 +8555,9 @@
         <v>889.030997061319</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A368" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B368">
         <v>900.90204254142805</v>
@@ -8572,9 +8569,9 @@
         <v>397.53986380421901</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A369" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B369">
         <v>24.753308530380298</v>
@@ -8586,9 +8583,9 @@
         <v>37.578573516298803</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A370" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B370">
         <v>623.32466354779399</v>
@@ -8600,9 +8597,9 @@
         <v>856.39063782277105</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A371" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B371">
         <v>305.12519348399599</v>
@@ -8614,9 +8611,9 @@
         <v>815.54017754587699</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A372" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B372">
         <v>540.40102243260799</v>
@@ -8628,9 +8625,9 @@
         <v>141.66487931787501</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A373" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B373">
         <v>621.23517418276504</v>
@@ -8642,9 +8639,9 @@
         <v>614.95695040783005</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A374" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B374">
         <v>47.436969614154698</v>
@@ -8656,9 +8653,9 @@
         <v>981.69852934574396</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A375" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B375">
         <v>70.457636954483306</v>
@@ -8670,9 +8667,9 @@
         <v>92.283261422201306</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A376" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B376">
         <v>986.76030569195495</v>
@@ -8684,9 +8681,9 @@
         <v>649.248663212785</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A377" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B377">
         <v>120.42051026151699</v>
@@ -8698,9 +8695,9 @@
         <v>183.867365187866</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A378" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B378">
         <v>303.78220019697397</v>
@@ -8712,9 +8709,9 @@
         <v>595.82501970500596</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A379" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B379">
         <v>789.72136585481201</v>
@@ -8726,9 +8723,9 @@
         <v>946.61026948036499</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A380" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B380">
         <v>384.32141265388202</v>
@@ -8740,9 +8737,9 @@
         <v>286.61270727356901</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A381" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B381">
         <v>728.16038207737904</v>
@@ -8754,9 +8751,9 @@
         <v>786.575818282814</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A382" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B382">
         <v>872.28291556899705</v>
@@ -8768,9 +8765,9 @@
         <v>733.78821378979205</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A383" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B383">
         <v>818.61064682193296</v>
@@ -8782,9 +8779,9 @@
         <v>413.34638653046198</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A384" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B384">
         <v>353.34810919506401</v>
@@ -8796,9 +8793,9 @@
         <v>587.849575935183</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A385" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B385">
         <v>932.72506773651799</v>
@@ -8810,9 +8807,9 @@
         <v>409.72908999077902</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A386" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B386">
         <v>681.03485231815</v>
@@ -8824,9 +8821,9 @@
         <v>978.03354103439301</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A387" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B387">
         <v>568.43825601756998</v>
@@ -8838,9 +8835,9 @@
         <v>811.60315305328697</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A388" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B388">
         <v>734.50636535698197</v>
@@ -8852,9 +8849,9 @@
         <v>125.053247265503</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A389" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B389">
         <v>155.046299874493</v>
@@ -8866,9 +8863,9 @@
         <v>81.819799654342404</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A390" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B390">
         <v>509.662434959027</v>
@@ -8880,9 +8877,9 @@
         <v>994.49381570254502</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A391" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B391">
         <v>325.15442115147499</v>
@@ -8894,9 +8891,9 @@
         <v>621.251425525169</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A392" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B392">
         <v>502.336476102181</v>
@@ -8908,9 +8905,9 @@
         <v>279.89775004133202</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A393" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B393">
         <v>751.48809103947497</v>
@@ -8922,9 +8919,9 @@
         <v>547.80321463013195</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A394" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B394">
         <v>712.87959454334396</v>
@@ -8936,9 +8933,9 @@
         <v>674.69312069895</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A395" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B395">
         <v>214.81312410265701</v>
@@ -8950,9 +8947,9 @@
         <v>231.95497749131201</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A396" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B396">
         <v>229.786279163693</v>
@@ -8964,9 +8961,9 @@
         <v>710.00521285629202</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A397" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B397">
         <v>463.897989892586</v>
@@ -8978,9 +8975,9 @@
         <v>478.24642303509802</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A398" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B398">
         <v>366.16906133689099</v>
@@ -8992,9 +8989,9 @@
         <v>16.047130827676</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A399" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B399">
         <v>104.738433855005</v>
@@ -9006,9 +9003,9 @@
         <v>137.594375636677</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A400" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B400">
         <v>98.488229444630093</v>
@@ -9020,9 +9017,9 @@
         <v>847.015753330905</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A401" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B401">
         <v>431.29494040457803</v>
@@ -9034,9 +9031,9 @@
         <v>390.50109479644999</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A402" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B402">
         <v>320.714069125896</v>
@@ -9048,9 +9045,9 @@
         <v>421.43808060996099</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A403" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B403">
         <v>215.205251871294</v>
@@ -9062,9 +9059,9 @@
         <v>203.03754669338801</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A404" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B404">
         <v>0.58640363990503097</v>
@@ -9076,9 +9073,9 @@
         <v>619.05713773525804</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A405" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B405">
         <v>117.15720692652999</v>
@@ -9090,9 +9087,9 @@
         <v>124.295514236476</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A406" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B406">
         <v>770.57953571196504</v>
@@ -9104,9 +9101,9 @@
         <v>982.91971297350904</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A407" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B407">
         <v>887.06790478758899</v>
@@ -9118,9 +9115,9 @@
         <v>308.73881262087701</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A408" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B408">
         <v>315.85484625320601</v>
@@ -9132,9 +9129,9 @@
         <v>59.794941182822903</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A409" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B409">
         <v>960.41059261107603</v>
@@ -9146,9 +9143,9 @@
         <v>101.66339838598</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A410" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B410">
         <v>577.53313017812195</v>
@@ -9160,9 +9157,9 @@
         <v>33.790875282022199</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A411" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B411">
         <v>720.09717035910501</v>
@@ -9174,9 +9171,9 @@
         <v>656.74972055383898</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A412" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B412">
         <v>190.27281823682901</v>
@@ -9188,9 +9185,9 @@
         <v>296.72412916526298</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A413" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B413">
         <v>353.34707152297398</v>
@@ -9202,9 +9199,9 @@
         <v>260.330344961425</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A414" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B414">
         <v>109.49685915605301</v>
@@ -9216,9 +9213,9 @@
         <v>505.03855428077702</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A415" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B415">
         <v>874.25558990254797</v>
@@ -9230,9 +9227,9 @@
         <v>20.019644494881401</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A416" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B416">
         <v>799.71320171275795</v>
@@ -9244,9 +9241,9 @@
         <v>205.84769769229899</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A417" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B417">
         <v>80.681716011205097</v>
@@ -9258,9 +9255,9 @@
         <v>896.11290196743903</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A418" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B418">
         <v>687.15733475979403</v>
@@ -9272,9 +9269,9 @@
         <v>633.66945791618195</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A419" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B419">
         <v>889.85082711067901</v>
@@ -9286,9 +9283,9 @@
         <v>558.55049395480103</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A420" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B420">
         <v>806.52955513949996</v>
@@ -9300,9 +9297,9 @@
         <v>74.549192744671998</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A421" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B421">
         <v>762.57678787053601</v>
@@ -9314,9 +9311,9 @@
         <v>581.53603504756904</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A422" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B422">
         <v>334.50631190828602</v>
@@ -9328,9 +9325,9 @@
         <v>106.375036487592</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A423" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B423">
         <v>207.16443369452401</v>
@@ -9342,9 +9339,9 @@
         <v>786.22874008610904</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A424" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B424">
         <v>497.19799149287701</v>
@@ -9356,9 +9353,9 @@
         <v>624.11748426534302</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A425" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B425">
         <v>987.80511925132305</v>
@@ -9370,9 +9367,9 @@
         <v>136.69017834100899</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A426" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B426">
         <v>400.49307085191401</v>
@@ -9384,9 +9381,9 @@
         <v>325.41355891623999</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A427" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B427">
         <v>175.48098927148101</v>
@@ -9398,9 +9395,9 @@
         <v>178.55969280197399</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A428" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B428">
         <v>159.97346129495401</v>
@@ -9412,9 +9409,9 @@
         <v>366.03864935517697</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A429" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B429">
         <v>74.979653205367399</v>
@@ -9426,9 +9423,9 @@
         <v>621.88861494034097</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A430" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B430">
         <v>206.19578974529199</v>
